--- a/data/trans_bre/P0901-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P0901-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 12,47</t>
+          <t>6,22; 12,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 16,6</t>
+          <t>8,44; 16,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 18,19</t>
+          <t>9,59; 18,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,9; 18,5</t>
+          <t>9,17; 18,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,55; 80,97</t>
+          <t>33,88; 83,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,44; 74,23</t>
+          <t>29,95; 73,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,05; 87,68</t>
+          <t>38,76; 89,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,68; 70,01</t>
+          <t>28,01; 67,78</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,51</t>
+          <t>2,83; 6,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,46</t>
+          <t>2,71; 6,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,94</t>
+          <t>4,03; 8,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,29</t>
+          <t>-0,98; 6,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,11; 134,97</t>
+          <t>44,17; 132,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,39; 101,44</t>
+          <t>33,66; 112,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,41; 122,59</t>
+          <t>49,93; 126,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 74,26</t>
+          <t>-7,17; 71,55</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 8,08</t>
+          <t>1,38; 7,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 5,36</t>
+          <t>-2,03; 5,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,3</t>
+          <t>0,97; 8,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,57</t>
+          <t>-1,14; 4,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,58; 240,36</t>
+          <t>17,18; 235,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 129,59</t>
+          <t>-26,44; 120,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,87; 199,89</t>
+          <t>9,81; 212,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 73,35</t>
+          <t>-13,18; 71,36</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,85</t>
+          <t>5,77; 8,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,51</t>
+          <t>7,04; 10,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,6</t>
+          <t>7,11; 10,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,54</t>
+          <t>2,72; 9,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,89; 105,6</t>
+          <t>59,29; 107,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,22; 94,01</t>
+          <t>54,63; 94,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,19; 107,85</t>
+          <t>63,75; 109,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,7; 78,62</t>
+          <t>20,99; 83,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P0901-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P0901-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>14,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,54</t>
+          <t>5,93; 12,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 16,58</t>
+          <t>8,52; 16,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 18,5</t>
+          <t>9,16; 18,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 18,38</t>
+          <t>10,05; 19,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,88; 83,86</t>
+          <t>31,71; 81,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,95; 73,26</t>
+          <t>31,31; 72,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,76; 89,61</t>
+          <t>35,51; 87,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,01; 67,78</t>
+          <t>32,45; 75,8</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>3,84</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,36</t>
+          <t>2,58; 6,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,69</t>
+          <t>2,67; 6,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,12</t>
+          <t>4,0; 8,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 6,12</t>
+          <t>1,77; 5,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,17; 132,77</t>
+          <t>39,76; 132,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,66; 112,19</t>
+          <t>31,86; 102,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,93; 126,71</t>
+          <t>50,43; 123,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 71,55</t>
+          <t>13,46; 53,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,75</t>
+          <t>1,53; 8,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 5,05</t>
+          <t>-1,76; 5,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,58</t>
+          <t>1,37; 8,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,54</t>
+          <t>-0,1; 5,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,18; 235,44</t>
+          <t>24,12; 261,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 120,44</t>
+          <t>-23,38; 118,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 212,43</t>
+          <t>18,83; 205,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 71,36</t>
+          <t>-1,58; 92,38</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,97</t>
+          <t>5,71; 9,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,62</t>
+          <t>6,89; 10,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 10,87</t>
+          <t>7,11; 10,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,09</t>
+          <t>5,33; 8,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,29; 107,94</t>
+          <t>58,13; 109,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,63; 94,9</t>
+          <t>54,05; 94,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,75; 109,75</t>
+          <t>62,48; 112,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,99; 83,47</t>
+          <t>36,07; 67,19</t>
         </is>
       </c>
     </row>
